--- a/Stats Sheet/Round Gaps/Peaks and Valleys.xlsx
+++ b/Stats Sheet/Round Gaps/Peaks and Valleys.xlsx
@@ -427,7 +427,7 @@
     <x:t>Guardaxion</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>Westcraft00</x:t>
